--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/region-de-antofagasta.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/region-de-antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>881-232-CM26</t>
+          <t>3506-18-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,372 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>82755.27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3834-54-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SUPER SOFTWARE SPA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>34510</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2385-348-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>1692.08</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1375735-46-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.981.250-6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Netsus SpA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>11186</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2429-2562-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>8205.219999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2429-2563-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>29304.35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>881-232-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>72.224.100-2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Site Chile Sociedad Anónima</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>96.988.790-8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>1547</v>
       </c>
     </row>
